--- a/AAII_Financials/Yearly/GRML_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRML_YR_FIN.xlsx
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
         <v>1300</v>
